--- a/Supplemental_data/Supplemental data 14.xlsx
+++ b/Supplemental_data/Supplemental data 14.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="551">
   <si>
-    <t>Shared DEDMGs that were upregulated or downregulated in both ecotypes, and hyper- and /or hypomethylated in the same sequence context and genic region</t>
+    <t xml:space="preserve">Shared differentially expressed differentially methylated genes with similar regulation between ecotypes, and similar methylation patterns in regions and contexts. </t>
   </si>
   <si>
     <t>Expression data for each ecotype follows the same order as the ecotype positions in column A</t>

--- a/Supplemental_data/Supplemental data 14.xlsx
+++ b/Supplemental_data/Supplemental data 14.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="550">
   <si>
     <t xml:space="preserve">Shared differentially expressed differentially methylated genes with similar regulation between ecotypes, and similar methylation patterns in regions and contexts. </t>
   </si>
@@ -1492,9 +1492,6 @@
   </si>
   <si>
     <t>sec7 domain-containing protein</t>
-  </si>
-  <si>
-    <t>Alta leafta crown_Alta leaf</t>
   </si>
   <si>
     <t>FvH4_6g03051</t>
@@ -1825,7 +1822,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1905,6 +1902,9 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -18400,6 +18400,9 @@
       <c r="H3" s="17" t="s">
         <v>160</v>
       </c>
+      <c r="I3" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="19"/>
@@ -18424,6 +18427,9 @@
       <c r="H4" s="17" t="s">
         <v>160</v>
       </c>
+      <c r="I4" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="19"/>
@@ -18448,6 +18454,9 @@
       <c r="H5" s="17" t="s">
         <v>160</v>
       </c>
+      <c r="I5" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="19"/>
@@ -18472,6 +18481,9 @@
       <c r="H6" s="17" t="s">
         <v>160</v>
       </c>
+      <c r="I6" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="19"/>
@@ -18496,6 +18508,9 @@
       <c r="H7" s="17" t="s">
         <v>160</v>
       </c>
+      <c r="I7" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="19"/>
@@ -18520,6 +18535,9 @@
       <c r="H8" s="17" t="s">
         <v>160</v>
       </c>
+      <c r="I8" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="19"/>
@@ -18544,6 +18562,9 @@
       <c r="H9" s="17" t="s">
         <v>160</v>
       </c>
+      <c r="I9" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="19"/>
@@ -18568,6 +18589,9 @@
       <c r="H10" s="17" t="s">
         <v>160</v>
       </c>
+      <c r="I10" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="19"/>
@@ -18592,6 +18616,9 @@
       <c r="H11" s="17" t="s">
         <v>160</v>
       </c>
+      <c r="I11" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="19"/>
@@ -18616,6 +18643,9 @@
       <c r="H12" s="17" t="s">
         <v>160</v>
       </c>
+      <c r="I12" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="19"/>
@@ -18640,6 +18670,9 @@
       <c r="H13" s="17" t="s">
         <v>165</v>
       </c>
+      <c r="I13" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="19"/>
@@ -18664,6 +18697,9 @@
       <c r="H14" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I14" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="19"/>
@@ -18682,11 +18718,14 @@
       <c r="F15" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="32" t="s">
+      <c r="G15" s="33" t="s">
         <v>87</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I15" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
@@ -18712,6 +18751,9 @@
       <c r="H16" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I16" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="19"/>
@@ -18736,6 +18778,9 @@
       <c r="H17" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I17" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="19"/>
@@ -18760,6 +18805,9 @@
       <c r="H18" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I18" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="19"/>
@@ -18784,6 +18832,9 @@
       <c r="H19" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I19" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="19"/>
@@ -18808,6 +18859,9 @@
       <c r="H20" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I20" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="19"/>
@@ -18832,6 +18886,9 @@
       <c r="H21" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I21" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="19"/>
@@ -18856,6 +18913,9 @@
       <c r="H22" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I22" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="19"/>
@@ -18880,6 +18940,9 @@
       <c r="H23" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I23" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="19"/>
@@ -18904,6 +18967,9 @@
       <c r="H24" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I24" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="19"/>
@@ -18928,6 +18994,9 @@
       <c r="H25" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I25" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="19"/>
@@ -18952,6 +19021,9 @@
       <c r="H26" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I26" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="19"/>
@@ -18976,6 +19048,9 @@
       <c r="H27" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I27" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="19"/>
@@ -19000,6 +19075,9 @@
       <c r="H28" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I28" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="21"/>
@@ -19024,6 +19102,9 @@
       <c r="H29" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I29" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="14" t="s">
@@ -19106,7 +19187,7 @@
       <c r="B33" s="15" t="s">
         <v>380</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="C33" s="34" t="s">
         <v>381</v>
       </c>
       <c r="D33" s="23">
@@ -19149,6 +19230,9 @@
       </c>
       <c r="H34" s="17" t="s">
         <v>160</v>
+      </c>
+      <c r="I34" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
@@ -19174,6 +19258,9 @@
       <c r="H35" s="17" t="s">
         <v>160</v>
       </c>
+      <c r="I35" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="19"/>
@@ -19198,6 +19285,9 @@
       <c r="H36" s="17" t="s">
         <v>165</v>
       </c>
+      <c r="I36" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="19"/>
@@ -19222,6 +19312,9 @@
       <c r="H37" s="17" t="s">
         <v>165</v>
       </c>
+      <c r="I37" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="19"/>
@@ -19246,6 +19339,9 @@
       <c r="H38" s="17" t="s">
         <v>165</v>
       </c>
+      <c r="I38" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="19"/>
@@ -19270,6 +19366,9 @@
       <c r="H39" s="17" t="s">
         <v>165</v>
       </c>
+      <c r="I39" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="19"/>
@@ -19294,6 +19393,9 @@
       <c r="H40" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I40" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="19"/>
@@ -19318,6 +19420,9 @@
       <c r="H41" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I41" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="19"/>
@@ -19342,6 +19447,9 @@
       <c r="H42" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I42" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="19"/>
@@ -19366,6 +19474,9 @@
       <c r="H43" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I43" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="19"/>
@@ -19390,6 +19501,9 @@
       <c r="H44" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I44" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="19"/>
@@ -19414,6 +19528,9 @@
       <c r="H45" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I45" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="19"/>
@@ -19438,6 +19555,9 @@
       <c r="H46" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I46" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="19"/>
@@ -19462,6 +19582,9 @@
       <c r="H47" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I47" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="19"/>
@@ -19486,6 +19609,9 @@
       <c r="H48" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I48" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="19"/>
@@ -19510,6 +19636,9 @@
       <c r="H49" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I49" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="19"/>
@@ -19534,6 +19663,9 @@
       <c r="H50" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I50" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="19"/>
@@ -19558,6 +19690,9 @@
       <c r="H51" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I51" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="19"/>
@@ -19582,13 +19717,16 @@
       <c r="H52" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I52" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="21"/>
       <c r="B53" s="15" t="s">
         <v>414</v>
       </c>
-      <c r="C53" s="33" t="s">
+      <c r="C53" s="34" t="s">
         <v>415</v>
       </c>
       <c r="D53" s="23">
@@ -19605,6 +19743,9 @@
       </c>
       <c r="H53" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I53" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
@@ -19632,6 +19773,7 @@
       <c r="H54" s="17" t="s">
         <v>160</v>
       </c>
+      <c r="I54" s="32"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="19"/>
@@ -19760,7 +19902,7 @@
       <c r="B60" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="C60" s="33" t="s">
+      <c r="C60" s="34" t="s">
         <v>425</v>
       </c>
       <c r="D60" s="23">
@@ -19803,6 +19945,9 @@
       </c>
       <c r="H61" s="17" t="s">
         <v>160</v>
+      </c>
+      <c r="I61" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -19828,6 +19973,9 @@
       <c r="H62" s="17" t="s">
         <v>160</v>
       </c>
+      <c r="I62" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="19"/>
@@ -19852,6 +20000,9 @@
       <c r="H63" s="17" t="s">
         <v>160</v>
       </c>
+      <c r="I63" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="19"/>
@@ -19876,6 +20027,9 @@
       <c r="H64" s="17" t="s">
         <v>160</v>
       </c>
+      <c r="I64" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="19"/>
@@ -19900,6 +20054,9 @@
       <c r="H65" s="17" t="s">
         <v>165</v>
       </c>
+      <c r="I65" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="19"/>
@@ -19924,6 +20081,9 @@
       <c r="H66" s="17" t="s">
         <v>165</v>
       </c>
+      <c r="I66" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="19"/>
@@ -19948,6 +20108,9 @@
       <c r="H67" s="17" t="s">
         <v>165</v>
       </c>
+      <c r="I67" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="19"/>
@@ -19972,6 +20135,9 @@
       <c r="H68" s="17" t="s">
         <v>165</v>
       </c>
+      <c r="I68" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="19"/>
@@ -19996,6 +20162,9 @@
       <c r="H69" s="17" t="s">
         <v>165</v>
       </c>
+      <c r="I69" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="19"/>
@@ -20020,6 +20189,9 @@
       <c r="H70" s="17" t="s">
         <v>165</v>
       </c>
+      <c r="I70" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="19"/>
@@ -20044,6 +20216,9 @@
       <c r="H71" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I71" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="19"/>
@@ -20068,6 +20243,9 @@
       <c r="H72" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I72" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="19"/>
@@ -20092,6 +20270,9 @@
       <c r="H73" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I73" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="19"/>
@@ -20116,6 +20297,9 @@
       <c r="H74" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I74" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="19"/>
@@ -20140,6 +20324,9 @@
       <c r="H75" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I75" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="19"/>
@@ -20164,6 +20351,9 @@
       <c r="H76" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I76" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="19"/>
@@ -20188,6 +20378,9 @@
       <c r="H77" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I77" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="19"/>
@@ -20212,6 +20405,9 @@
       <c r="H78" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I78" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="19"/>
@@ -20236,6 +20432,9 @@
       <c r="H79" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I79" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="19"/>
@@ -20260,6 +20459,9 @@
       <c r="H80" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I80" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="19"/>
@@ -20284,6 +20486,9 @@
       <c r="H81" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I81" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="19"/>
@@ -20308,6 +20513,9 @@
       <c r="H82" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I82" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="19"/>
@@ -20332,6 +20540,9 @@
       <c r="H83" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I83" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="19"/>
@@ -20356,6 +20567,9 @@
       <c r="H84" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I84" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="19"/>
@@ -20380,6 +20594,9 @@
       <c r="H85" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I85" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="19"/>
@@ -20404,6 +20621,9 @@
       <c r="H86" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I86" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="19"/>
@@ -20428,6 +20648,9 @@
       <c r="H87" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I87" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="19"/>
@@ -20452,6 +20675,9 @@
       <c r="H88" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I88" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c r="A89" s="19"/>
@@ -20476,6 +20702,9 @@
       <c r="H89" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I89" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="90" ht="14.25" customHeight="1">
       <c r="A90" s="19"/>
@@ -20500,6 +20729,9 @@
       <c r="H90" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I90" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c r="A91" s="19"/>
@@ -20524,6 +20756,9 @@
       <c r="H91" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I91" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
       <c r="A92" s="19"/>
@@ -20548,6 +20783,9 @@
       <c r="H92" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I92" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="19"/>
@@ -20572,6 +20810,9 @@
       <c r="H93" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I93" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c r="A94" s="19"/>
@@ -20596,6 +20837,9 @@
       <c r="H94" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I94" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
       <c r="A95" s="19"/>
@@ -20620,6 +20864,9 @@
       <c r="H95" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I95" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
       <c r="A96" s="21"/>
@@ -20644,6 +20891,9 @@
       <c r="H96" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I96" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
       <c r="A97" s="14" t="s">
@@ -20798,7 +21048,7 @@
       <c r="B103" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="C103" s="33" t="s">
+      <c r="C103" s="34" t="s">
         <v>490</v>
       </c>
       <c r="D103" s="23">
@@ -20818,11 +21068,11 @@
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="14" t="s">
+      <c r="A104" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="B104" s="15" t="s">
         <v>491</v>
-      </c>
-      <c r="B104" s="15" t="s">
-        <v>492</v>
       </c>
       <c r="C104" s="30" t="s">
         <v>113</v>
@@ -20841,15 +21091,18 @@
       </c>
       <c r="H104" s="17" t="s">
         <v>160</v>
+      </c>
+      <c r="I104" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="105" ht="14.25" customHeight="1">
       <c r="A105" s="19"/>
       <c r="B105" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="C105" s="30" t="s">
         <v>493</v>
-      </c>
-      <c r="C105" s="30" t="s">
-        <v>494</v>
       </c>
       <c r="D105" s="23">
         <v>-3.44749</v>
@@ -20865,15 +21118,18 @@
       </c>
       <c r="H105" s="17" t="s">
         <v>160</v>
+      </c>
+      <c r="I105" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
       <c r="A106" s="19"/>
       <c r="B106" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="C106" s="30" t="s">
         <v>495</v>
-      </c>
-      <c r="C106" s="30" t="s">
-        <v>496</v>
       </c>
       <c r="D106" s="23">
         <v>-5.61482</v>
@@ -20889,15 +21145,18 @@
       </c>
       <c r="H106" s="17" t="s">
         <v>160</v>
+      </c>
+      <c r="I106" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
       <c r="A107" s="19"/>
       <c r="B107" s="15" t="s">
+        <v>496</v>
+      </c>
+      <c r="C107" s="30" t="s">
         <v>497</v>
-      </c>
-      <c r="C107" s="30" t="s">
-        <v>498</v>
       </c>
       <c r="D107" s="23">
         <v>-2.60785</v>
@@ -20913,6 +21172,9 @@
       </c>
       <c r="H107" s="17" t="s">
         <v>160</v>
+      </c>
+      <c r="I107" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -20938,11 +21200,14 @@
       <c r="H108" s="17" t="s">
         <v>160</v>
       </c>
+      <c r="I108" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
       <c r="A109" s="19"/>
       <c r="B109" s="15" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C109" s="30" t="s">
         <v>113</v>
@@ -20961,15 +21226,18 @@
       </c>
       <c r="H109" s="17" t="s">
         <v>165</v>
+      </c>
+      <c r="I109" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="110" ht="14.25" customHeight="1">
       <c r="A110" s="19"/>
       <c r="B110" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="C110" s="30" t="s">
         <v>500</v>
-      </c>
-      <c r="C110" s="30" t="s">
-        <v>501</v>
       </c>
       <c r="D110" s="23">
         <v>-6.48251</v>
@@ -20985,12 +21253,15 @@
       </c>
       <c r="H110" s="17" t="s">
         <v>165</v>
+      </c>
+      <c r="I110" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
       <c r="A111" s="19"/>
       <c r="B111" s="15" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C111" s="30" t="s">
         <v>242</v>
@@ -21009,6 +21280,9 @@
       </c>
       <c r="H111" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I111" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -21034,14 +21308,17 @@
       <c r="H112" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I112" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
       <c r="A113" s="19"/>
       <c r="B113" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="C113" s="30" t="s">
         <v>503</v>
-      </c>
-      <c r="C113" s="30" t="s">
-        <v>504</v>
       </c>
       <c r="D113" s="23">
         <v>-285.9678</v>
@@ -21057,15 +21334,18 @@
       </c>
       <c r="H113" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I113" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
       <c r="A114" s="19"/>
       <c r="B114" s="15" t="s">
+        <v>504</v>
+      </c>
+      <c r="C114" s="30" t="s">
         <v>505</v>
-      </c>
-      <c r="C114" s="30" t="s">
-        <v>506</v>
       </c>
       <c r="D114" s="23">
         <v>-2.85707</v>
@@ -21081,15 +21361,18 @@
       </c>
       <c r="H114" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I114" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="115" ht="14.25" customHeight="1">
       <c r="A115" s="19"/>
       <c r="B115" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C115" s="30" t="s">
         <v>507</v>
-      </c>
-      <c r="C115" s="30" t="s">
-        <v>508</v>
       </c>
       <c r="D115" s="23">
         <v>-2.4573</v>
@@ -21105,15 +21388,18 @@
       </c>
       <c r="H115" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I115" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
       <c r="A116" s="19"/>
       <c r="B116" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="C116" s="30" t="s">
         <v>509</v>
-      </c>
-      <c r="C116" s="30" t="s">
-        <v>510</v>
       </c>
       <c r="D116" s="23">
         <v>-2.77816</v>
@@ -21129,15 +21415,18 @@
       </c>
       <c r="H116" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I116" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
       <c r="A117" s="19"/>
       <c r="B117" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="C117" s="30" t="s">
         <v>511</v>
-      </c>
-      <c r="C117" s="30" t="s">
-        <v>512</v>
       </c>
       <c r="D117" s="23">
         <v>-14.51033</v>
@@ -21153,15 +21442,18 @@
       </c>
       <c r="H117" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I117" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
       <c r="A118" s="19"/>
       <c r="B118" s="15" t="s">
+        <v>512</v>
+      </c>
+      <c r="C118" s="30" t="s">
         <v>513</v>
-      </c>
-      <c r="C118" s="30" t="s">
-        <v>514</v>
       </c>
       <c r="D118" s="23">
         <v>-17.68449</v>
@@ -21177,15 +21469,18 @@
       </c>
       <c r="H118" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I118" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
       <c r="A119" s="19"/>
       <c r="B119" s="15" t="s">
+        <v>514</v>
+      </c>
+      <c r="C119" s="30" t="s">
         <v>515</v>
-      </c>
-      <c r="C119" s="30" t="s">
-        <v>516</v>
       </c>
       <c r="D119" s="23">
         <v>-75.78731</v>
@@ -21201,12 +21496,15 @@
       </c>
       <c r="H119" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I119" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="120" ht="14.25" customHeight="1">
       <c r="A120" s="19"/>
       <c r="B120" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C120" s="30" t="s">
         <v>314</v>
@@ -21225,15 +21523,18 @@
       </c>
       <c r="H120" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I120" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
       <c r="A121" s="19"/>
       <c r="B121" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="C121" s="30" t="s">
         <v>518</v>
-      </c>
-      <c r="C121" s="30" t="s">
-        <v>519</v>
       </c>
       <c r="D121" s="23">
         <v>-3.24041</v>
@@ -21249,15 +21550,18 @@
       </c>
       <c r="H121" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I121" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
       <c r="A122" s="19"/>
       <c r="B122" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="C122" s="30" t="s">
         <v>520</v>
-      </c>
-      <c r="C122" s="30" t="s">
-        <v>521</v>
       </c>
       <c r="D122" s="23">
         <v>-14.83865</v>
@@ -21273,6 +21577,9 @@
       </c>
       <c r="H122" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I122" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -21298,14 +21605,17 @@
       <c r="H123" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I123" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
       <c r="A124" s="19"/>
       <c r="B124" s="15" t="s">
+        <v>521</v>
+      </c>
+      <c r="C124" s="30" t="s">
         <v>522</v>
-      </c>
-      <c r="C124" s="30" t="s">
-        <v>523</v>
       </c>
       <c r="D124" s="23">
         <v>-46.49786</v>
@@ -21321,15 +21631,18 @@
       </c>
       <c r="H124" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I124" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="125" ht="14.25" customHeight="1">
       <c r="A125" s="19"/>
       <c r="B125" s="15" t="s">
+        <v>523</v>
+      </c>
+      <c r="C125" s="30" t="s">
         <v>524</v>
-      </c>
-      <c r="C125" s="30" t="s">
-        <v>525</v>
       </c>
       <c r="D125" s="23">
         <v>-3.81679</v>
@@ -21345,15 +21658,18 @@
       </c>
       <c r="H125" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I125" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
       <c r="A126" s="19"/>
       <c r="B126" s="15" t="s">
+        <v>525</v>
+      </c>
+      <c r="C126" s="30" t="s">
         <v>526</v>
-      </c>
-      <c r="C126" s="30" t="s">
-        <v>527</v>
       </c>
       <c r="D126" s="23">
         <v>-2.97985</v>
@@ -21369,6 +21685,9 @@
       </c>
       <c r="H126" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I126" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -21394,14 +21713,17 @@
       <c r="H127" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I127" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
       <c r="A128" s="19"/>
       <c r="B128" s="15" t="s">
+        <v>527</v>
+      </c>
+      <c r="C128" s="30" t="s">
         <v>528</v>
-      </c>
-      <c r="C128" s="30" t="s">
-        <v>529</v>
       </c>
       <c r="D128" s="23">
         <v>-4.49192</v>
@@ -21417,15 +21739,18 @@
       </c>
       <c r="H128" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I128" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
       <c r="A129" s="19"/>
       <c r="B129" s="15" t="s">
+        <v>529</v>
+      </c>
+      <c r="C129" s="30" t="s">
         <v>530</v>
-      </c>
-      <c r="C129" s="30" t="s">
-        <v>531</v>
       </c>
       <c r="D129" s="23">
         <v>-4.14615</v>
@@ -21441,15 +21766,18 @@
       </c>
       <c r="H129" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I129" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="130" ht="14.25" customHeight="1">
       <c r="A130" s="19"/>
       <c r="B130" s="15" t="s">
+        <v>531</v>
+      </c>
+      <c r="C130" s="30" t="s">
         <v>532</v>
-      </c>
-      <c r="C130" s="30" t="s">
-        <v>533</v>
       </c>
       <c r="D130" s="23">
         <v>-3.13039</v>
@@ -21465,6 +21793,9 @@
       </c>
       <c r="H130" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I130" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -21490,6 +21821,9 @@
       <c r="H131" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I131" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
       <c r="A132" s="19"/>
@@ -21514,14 +21848,17 @@
       <c r="H132" s="17" t="s">
         <v>170</v>
       </c>
+      <c r="I132" s="32">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
       <c r="A133" s="19"/>
       <c r="B133" s="15" t="s">
+        <v>533</v>
+      </c>
+      <c r="C133" s="30" t="s">
         <v>534</v>
-      </c>
-      <c r="C133" s="30" t="s">
-        <v>535</v>
       </c>
       <c r="D133" s="23">
         <v>-5.12135</v>
@@ -21537,15 +21874,18 @@
       </c>
       <c r="H133" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I133" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
       <c r="A134" s="19"/>
       <c r="B134" s="15" t="s">
+        <v>535</v>
+      </c>
+      <c r="C134" s="30" t="s">
         <v>536</v>
-      </c>
-      <c r="C134" s="30" t="s">
-        <v>537</v>
       </c>
       <c r="D134" s="23">
         <v>-4.45294</v>
@@ -21561,15 +21901,18 @@
       </c>
       <c r="H134" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I134" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="135" ht="14.25" customHeight="1">
       <c r="A135" s="19"/>
       <c r="B135" s="15" t="s">
+        <v>537</v>
+      </c>
+      <c r="C135" s="30" t="s">
         <v>538</v>
-      </c>
-      <c r="C135" s="30" t="s">
-        <v>539</v>
       </c>
       <c r="D135" s="23">
         <v>-2.42742</v>
@@ -21585,15 +21928,18 @@
       </c>
       <c r="H135" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I135" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
       <c r="A136" s="19"/>
       <c r="B136" s="15" t="s">
+        <v>539</v>
+      </c>
+      <c r="C136" s="30" t="s">
         <v>540</v>
-      </c>
-      <c r="C136" s="30" t="s">
-        <v>541</v>
       </c>
       <c r="D136" s="23">
         <v>-2.84358</v>
@@ -21609,15 +21955,18 @@
       </c>
       <c r="H136" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I136" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
       <c r="A137" s="21"/>
       <c r="B137" s="15" t="s">
+        <v>541</v>
+      </c>
+      <c r="C137" s="30" t="s">
         <v>542</v>
-      </c>
-      <c r="C137" s="30" t="s">
-        <v>543</v>
       </c>
       <c r="D137" s="23">
         <v>-5.00713</v>
@@ -21633,6 +21982,9 @@
       </c>
       <c r="H137" s="17" t="s">
         <v>170</v>
+      </c>
+      <c r="I137" s="32">
+        <v>1.0</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -21640,10 +21992,10 @@
         <v>373</v>
       </c>
       <c r="B138" s="15" t="s">
+        <v>543</v>
+      </c>
+      <c r="C138" s="30" t="s">
         <v>544</v>
-      </c>
-      <c r="C138" s="30" t="s">
-        <v>545</v>
       </c>
       <c r="D138" s="23">
         <v>-3.73491</v>
@@ -21664,10 +22016,10 @@
     <row r="139" ht="14.25" customHeight="1">
       <c r="A139" s="21"/>
       <c r="B139" s="15" t="s">
+        <v>545</v>
+      </c>
+      <c r="C139" s="30" t="s">
         <v>546</v>
-      </c>
-      <c r="C139" s="30" t="s">
-        <v>547</v>
       </c>
       <c r="D139" s="23">
         <v>-35.36909</v>
@@ -21690,10 +22042,10 @@
         <v>379</v>
       </c>
       <c r="B140" s="15" t="s">
+        <v>547</v>
+      </c>
+      <c r="C140" s="30" t="s">
         <v>548</v>
-      </c>
-      <c r="C140" s="30" t="s">
-        <v>549</v>
       </c>
       <c r="D140" s="23">
         <v>-3.9674</v>
@@ -21714,7 +22066,7 @@
     <row r="141" ht="14.25" customHeight="1">
       <c r="A141" s="21"/>
       <c r="B141" s="15" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C141" s="15" t="s">
         <v>435</v>
